--- a/Thesis/Tables/UAV Mission Profile Constraints table.xlsx
+++ b/Thesis/Tables/UAV Mission Profile Constraints table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Desktop\UAV_Mission\Thesis\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5EA9831-C5A1-407F-9A03-E57041A97480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA7F476-1A68-4FEF-8789-6598EE1EA593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="4860" windowWidth="21600" windowHeight="11715" xr2:uid="{30816EF4-0897-48B4-8B1D-42E9BAB76C28}"/>
+    <workbookView xWindow="8220" yWindow="4500" windowWidth="21600" windowHeight="11715" xr2:uid="{30816EF4-0897-48B4-8B1D-42E9BAB76C28}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -462,12 +462,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2889A14C-8AAD-43A0-8922-ACFED3D1D4D2}">
   <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -499,7 +499,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -531,7 +531,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -539,19 +539,19 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="F3">
-        <v>1250</v>
+        <v>2800</v>
       </c>
       <c r="G3">
-        <v>2000</v>
+        <v>5100</v>
       </c>
       <c r="J3">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -559,19 +559,19 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>560</v>
       </c>
       <c r="F4">
-        <v>105</v>
+        <v>560</v>
       </c>
       <c r="G4">
-        <v>110</v>
+        <v>560</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -593,7 +593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
